--- a/Scripts/PowerShell/TA_LIST_Sanity_Smoke/TA_Inventory.xlsx
+++ b/Scripts/PowerShell/TA_LIST_Sanity_Smoke/TA_Inventory.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SQL\SQL\TA_LIST_Sanity_Smoke\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\SQL\SQL\TA_LIST_Sanity_Smoke\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973CD63F-8A88-41A5-97C5-651B99CC92E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{78089FF6-7BB2-4F84-B442-735277C975E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3570" yWindow="1500" windowWidth="33840" windowHeight="18345" xr2:uid="{A335B00C-45B9-4E5E-A3B5-1F7AF0E65152}"/>
+    <workbookView xWindow="2415" yWindow="1920" windowWidth="33840" windowHeight="18345" xr2:uid="{DD14D627-A3FE-4A5D-9B73-814B612A5E23}"/>
   </bookViews>
   <sheets>
     <sheet name="TA_Report" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="546">
   <si>
     <t>Actor</t>
   </si>
@@ -1382,10 +1382,10 @@
     <t>TC-150</t>
   </si>
   <si>
-    <t>Process Claim File Inzicht - CHA_IM001</t>
-  </si>
-  <si>
-    <t>Provider\ClaimFile\ProcessFile\CHA_IM001.feature</t>
+    <t>Process Claim File - CHA_IM001</t>
+  </si>
+  <si>
+    <t>Agent\ClaimFile\ProcessFile\CHA_IM001.feature</t>
   </si>
   <si>
     <t>TC-151</t>
@@ -1686,12 +1686,6 @@
   </si>
   <si>
     <t>Tomasz Smerdzyński</t>
-  </si>
-  <si>
-    <t>TC-157</t>
-  </si>
-  <si>
-    <t>Inzicht Pogo Test</t>
   </si>
 </sst>
 </file>
@@ -2120,8 +2114,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9C53C5-891F-4D0A-9D08-C04C2A64B43E}">
-  <dimension ref="A1:L158"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7E337D7-9E96-492C-A995-A6BFDFEDAA79}">
+  <dimension ref="A1:L157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
@@ -2132,7 +2126,7 @@
     <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="85.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="60.7109375" customWidth="1"/>
     <col min="10" max="10" width="40.7109375" customWidth="1"/>
     <col min="11" max="12" width="12.7109375" customWidth="1"/>
   </cols>
@@ -5340,7 +5334,7 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B151" t="s">
         <v>443</v>
@@ -5499,54 +5493,43 @@
         <v>464</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>19</v>
-      </c>
-      <c r="B158" t="s">
-        <v>546</v>
-      </c>
-      <c r="C158" t="s">
-        <v>547</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L1" xr:uid="{7E9C53C5-891F-4D0A-9D08-C04C2A64B43E}"/>
+  <autoFilter ref="A1:L1" xr:uid="{C7E337D7-9E96-492C-A995-A6BFDFEDAA79}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{6C4EFBD9-C7F9-4A97-A085-ED72FDEA00A8}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{7922B5A7-4A41-46BC-9E45-B28A49929C56}">
           <x14:formula1>
             <xm:f>Actors!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A158</xm:sqref>
+          <xm:sqref>A2:A157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{77CBE42D-79E0-4379-BC9D-4FE111122D3E}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{B7CBA8AC-4608-42E3-9EC5-B1E0B34005FC}">
           <x14:formula1>
             <xm:f>Domains!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{88DE764D-2024-4754-ADD4-F8B6D26108BB}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{9A2E40CD-CEDE-4501-9DAA-C23A4A572C06}">
           <x14:formula1>
             <xm:f>Test_Types!$A$2:$A$6</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{1B21077B-4E60-4356-9AD6-AF74E96581AD}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{FF3EA81F-D401-4EB7-9B6A-EF1F5CE18BB5}">
           <x14:formula1>
             <xm:f>Status_Options!$A$1:$A$6</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{0A73A4A1-F29E-4DED-BCC3-47557A7AAF8D}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{3565FC22-DC56-44E0-BD01-3548015BAEB8}">
           <x14:formula1>
             <xm:f>Team_Members!$A$2:$A$57</xm:f>
           </x14:formula1>
           <xm:sqref>G2:G157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{E1DCA9B4-7737-49B0-BEAF-EAEC8E97AEF9}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{99C5D2DC-47A7-45B2-B45B-7089A47120D1}">
           <x14:formula1>
             <xm:f>Priorities!$A$2:$A$5</xm:f>
           </x14:formula1>
@@ -5559,7 +5542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69CA6A03-606C-4335-94C5-B9FD9123C3A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B13EF2ED-F7B7-4B9D-9E90-4AC6110B609B}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5602,7 +5585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{093EA66A-3273-411C-B2E5-EE30005EDB6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B6D594-57C4-432F-AC0F-E4E3623E5683}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5664,7 +5647,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC9A0342-6992-4806-A859-C3BADA5F36A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAFC637A-74C2-414B-A32C-9ECB0A2FC336}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5734,7 +5717,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{383787E8-9061-4B99-B8B9-C2D9AD65BDD7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75E968FB-11E7-4DF8-875A-76FAF28DB2E4}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5782,7 +5765,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55393163-4D78-4833-B9E7-1C0FB0682F5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{853ED996-B569-455B-8F58-B300E00C3F74}">
   <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5875,7 +5858,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{512FAE44-3320-4B85-A2BA-93B75C838D66}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F12254-E0BB-4671-9ECA-DA68B9695C95}">
   <dimension ref="A1:A57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/Scripts/PowerShell/TA_LIST_Sanity_Smoke/TA_Inventory.xlsx
+++ b/Scripts/PowerShell/TA_LIST_Sanity_Smoke/TA_Inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\SQL\SQL\TA_LIST_Sanity_Smoke\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78089FF6-7BB2-4F84-B442-735277C975E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AAB02FD-E5DA-47B0-9AF9-456E4FA9FC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2415" yWindow="1920" windowWidth="33840" windowHeight="18345" xr2:uid="{DD14D627-A3FE-4A5D-9B73-814B612A5E23}"/>
+    <workbookView xWindow="2415" yWindow="1920" windowWidth="33840" windowHeight="18345" xr2:uid="{98A834BA-DB17-43E3-8C6F-F4CBDEBBF62B}"/>
   </bookViews>
   <sheets>
     <sheet name="TA_Report" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Team_Members" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TA_Report!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TA_Report!$A$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="541">
   <si>
     <t>Actor</t>
   </si>
@@ -86,6 +86,9 @@
     <t>ADO_Int</t>
   </si>
   <si>
+    <t>Related_TC</t>
+  </si>
+  <si>
     <t>Provider</t>
   </si>
   <si>
@@ -764,7 +767,7 @@
     <t>Login to Inzicht - Authenticator</t>
   </si>
   <si>
-    <t>Provider\\Login\\AuthenticatorLogin.feature</t>
+    <t>Provider\Login\AuthenticatorLogin.feature</t>
   </si>
   <si>
     <t>TC-084</t>
@@ -773,7 +776,7 @@
     <t>Login to Inzicht - Email</t>
   </si>
   <si>
-    <t>Provider\\Login\\EmailLogin.feature</t>
+    <t>Provider\Login\EmailLogin.feature</t>
   </si>
   <si>
     <t>TC-085</t>
@@ -782,7 +785,7 @@
     <t>Login to Inzicht - SMS</t>
   </si>
   <si>
-    <t>Provider\\Login\\SMSLogin.feature</t>
+    <t>Provider\Login\SMSLogin.feature</t>
   </si>
   <si>
     <t>TC-086</t>
@@ -800,7 +803,7 @@
     <t>Delete User</t>
   </si>
   <si>
-    <t>Admin\\User\\DeleteUser.feature</t>
+    <t>Admin\User\DeleteUser.feature</t>
   </si>
   <si>
     <t>TC-088</t>
@@ -893,7 +896,7 @@
     <t>Claim Search - From Form</t>
   </si>
   <si>
-    <t>Agent\\Claim\\Search\\ClaimSearchFromForm.feature</t>
+    <t>Agent\Claim\Search\ClaimSearchFromForm.feature</t>
   </si>
   <si>
     <t>TC-098</t>
@@ -902,7 +905,7 @@
     <t>Claim Search - From URI</t>
   </si>
   <si>
-    <t>Agent\\Claim\\Search\\ClaimSearchFromUri.feature</t>
+    <t>Agent\Claim\Search\ClaimSearchFromUri.feature</t>
   </si>
   <si>
     <t>TC-099</t>
@@ -911,7 +914,7 @@
     <t>Objection Reason Management</t>
   </si>
   <si>
-    <t>Agent\\Maintenance\\ObjectionReason.feature</t>
+    <t>Agent\Maintenance\ObjectionReason.feature</t>
   </si>
   <si>
     <t>TC-100</t>
@@ -920,7 +923,7 @@
     <t>Rule Interpretation Details</t>
   </si>
   <si>
-    <t>Agent\\RuleInterpreter\\RuleInterpretationDetails.feature</t>
+    <t>Agent\RuleInterpreter\RuleInterpretationDetails.feature</t>
   </si>
   <si>
     <t>TC-101</t>
@@ -929,7 +932,7 @@
     <t>Rule Interpreter</t>
   </si>
   <si>
-    <t>Agent\\RuleInterpreter\\RuleInterpreter.feature</t>
+    <t>Agent\RuleInterpreter\RuleInterpreter.feature</t>
   </si>
   <si>
     <t>TC-102</t>
@@ -938,7 +941,7 @@
     <t>Add New Rule</t>
   </si>
   <si>
-    <t>Agent\\Rules\\AddNewRule.feature</t>
+    <t>Agent\Rules\AddNewRule.feature</t>
   </si>
   <si>
     <t>TC-103</t>
@@ -947,7 +950,7 @@
     <t>Delete Rule</t>
   </si>
   <si>
-    <t>Agent\\Rules\\DeleteRule.feature</t>
+    <t>Agent\Rules\DeleteRule.feature</t>
   </si>
   <si>
     <t>TC-104</t>
@@ -956,7 +959,7 @@
     <t>Update Rule</t>
   </si>
   <si>
-    <t>Agent\\Rules\\UpdateRule.feature</t>
+    <t>Agent\Rules\UpdateRule.feature</t>
   </si>
   <si>
     <t>TC-105</t>
@@ -965,7 +968,7 @@
     <t>Block Claim Redelivery After 3 Address Changes</t>
   </si>
   <si>
-    <t>Provider\\Claim\\AddressChange\\BlockClaimRedeliveryByPostAfter3AddressChanges.feature</t>
+    <t>Provider\Claim\AddressChange\BlockClaimRedeliveryByPostAfter3AddressChanges.feature</t>
   </si>
   <si>
     <t>TC-106</t>
@@ -974,7 +977,7 @@
     <t>Correct Incorrect Post Code</t>
   </si>
   <si>
-    <t>Provider\\Claim\\AddressChange\\CorrectIncorrectPostCode.feature</t>
+    <t>Provider\Claim\AddressChange\CorrectIncorrectPostCode.feature</t>
   </si>
   <si>
     <t>TC-107</t>
@@ -983,7 +986,7 @@
     <t>Retrocessions - Add Retrocession</t>
   </si>
   <si>
-    <t>Provider\\Claim\\Retrocessions\\AddRetrocession.feature</t>
+    <t>Provider\Claim\Retrocessions\AddRetrocession.feature</t>
   </si>
   <si>
     <t>TC-108</t>
@@ -992,7 +995,7 @@
     <t>Retrocessions - View Retrocessions</t>
   </si>
   <si>
-    <t>Provider\\Claim\\Retrocessions\\ViewRetrocessions.feature</t>
+    <t>Provider\Claim\Retrocessions\ViewRetrocessions.feature</t>
   </si>
   <si>
     <t>TC-109</t>
@@ -1001,7 +1004,7 @@
     <t>HelpDesk - My Tickets</t>
   </si>
   <si>
-    <t>Agent\\HelpdeskTOFIXPREPAREFOREMPTYENVIRONMENT\\MyTicketsPage.feature</t>
+    <t>Agent\HelpdeskTOFIXPREPAREFOREMPTYENVIRONMENT\MyTicketsPage.feature</t>
   </si>
   <si>
     <t>TC-110</t>
@@ -1010,7 +1013,7 @@
     <t>HelpDesk - Open Tickets</t>
   </si>
   <si>
-    <t>Agent\\HelpdeskTOFIXPREPAREFOREMPTYENVIRONMENT\\OpenTicketsPage.feature</t>
+    <t>Agent\HelpdeskTOFIXPREPAREFOREMPTYENVIRONMENT\OpenTicketsPage.feature</t>
   </si>
   <si>
     <t>TC-111</t>
@@ -1019,7 +1022,7 @@
     <t>HelpDesk - Ticket Page</t>
   </si>
   <si>
-    <t>Agent\\HelpdeskTOFIXPREPAREFOREMPTYENVIRONMENT\\TicketPage.feature</t>
+    <t>Agent\HelpdeskTOFIXPREPAREFOREMPTYENVIRONMENT\TicketPage.feature</t>
   </si>
   <si>
     <t>TC-112</t>
@@ -1028,7 +1031,7 @@
     <t>[TO REMOVE] Navigate to Incorrect Claims and Back</t>
   </si>
   <si>
-    <t>Provider\\NavigationTOREMOVEMAYBE\\NavigateToIncorrectClaimsAndBack.feature</t>
+    <t>Provider\NavigationTOREMOVEMAYBE\NavigateToIncorrectClaimsAndBack.feature</t>
   </si>
   <si>
     <t>TC-113</t>
@@ -1037,7 +1040,7 @@
     <t>[TO REMOVE] Navigate from BA Overview</t>
   </si>
   <si>
-    <t>Provider\\NavigationTOREMOVEMAYBE\\NavigateToIncorrectClaimsFromBAOverview.feature</t>
+    <t>Provider\NavigationTOREMOVEMAYBE\NavigateToIncorrectClaimsFromBAOverview.feature</t>
   </si>
   <si>
     <t>TC-114</t>
@@ -1046,7 +1049,7 @@
     <t>[TO REMOVE] Navigate from First Row</t>
   </si>
   <si>
-    <t>Provider\\NavigationTOREMOVEMAYBE\\NavigateToIncorrectClaimsFromFirstRow.feature</t>
+    <t>Provider\NavigationTOREMOVEMAYBE\NavigateToIncorrectClaimsFromFirstRow.feature</t>
   </si>
   <si>
     <t>TC-115</t>
@@ -1058,7 +1061,7 @@
     <t>Costs &amp; Tariffs</t>
   </si>
   <si>
-    <t>Agent\\BulkFee\\ApproveFee.feature</t>
+    <t>Agent\BulkFee\ApproveFee.feature</t>
   </si>
   <si>
     <t>TC-116</t>
@@ -1067,7 +1070,7 @@
     <t>Decline Bulk Fee</t>
   </si>
   <si>
-    <t>Agent\\BulkFee\\DeclineFee.feature</t>
+    <t>Agent\BulkFee\DeclineFee.feature</t>
   </si>
   <si>
     <t>TC-117</t>
@@ -1079,7 +1082,7 @@
     <t>Customer Configuration</t>
   </si>
   <si>
-    <t>Agent\\BusinessAccount\\SpecialAgreementNote.feature</t>
+    <t>Agent\BusinessAccount\SpecialAgreementNote.feature</t>
   </si>
   <si>
     <t>TC-118</t>
@@ -1100,7 +1103,7 @@
     <t>Postpone Invoice Due Date</t>
   </si>
   <si>
-    <t>Patient\\Claim\\ExtendDueDate\\PostponeInvoiceDueDate.feature</t>
+    <t>Patient\Claim\ExtendDueDate\PostponeInvoiceDueDate.feature</t>
   </si>
   <si>
     <t>TC-120</t>
@@ -1109,7 +1112,7 @@
     <t>Open Payment Page - Pharmaceutical Invoice</t>
   </si>
   <si>
-    <t>Patient\\Claim\\ShowClaim\\OpenPaymentPageForPharmaceuticalInvoice.feature</t>
+    <t>Patient\Claim\ShowClaim\OpenPaymentPageForPharmaceuticalInvoice.feature</t>
   </si>
   <si>
     <t>TC-121</t>
@@ -1118,7 +1121,7 @@
     <t>Open Payment Page - From Fallback Page</t>
   </si>
   <si>
-    <t>Patient\\Claim\\ShowClaim\\OpenPaymentPageFromFallbackPage.feature</t>
+    <t>Patient\Claim\ShowClaim\OpenPaymentPageFromFallbackPage.feature</t>
   </si>
   <si>
     <t>TC-122</t>
@@ -1127,7 +1130,7 @@
     <t>Open Payment Page - From URL</t>
   </si>
   <si>
-    <t>Patient\\Claim\\ShowClaim\\OpenPaymentPageFromUrl.feature</t>
+    <t>Patient\Claim\ShowClaim\OpenPaymentPageFromUrl.feature</t>
   </si>
   <si>
     <t>TC-123</t>
@@ -1136,7 +1139,7 @@
     <t>Open Payment Page - Invalid Invoice Number</t>
   </si>
   <si>
-    <t>Patient\\Claim\\ShowClaim\\OpenPaymentPageWithInvalidInvoiceNumber.feature</t>
+    <t>Patient\Claim\ShowClaim\OpenPaymentPageWithInvalidInvoiceNumber.feature</t>
   </si>
   <si>
     <t>TC-124</t>
@@ -1145,7 +1148,7 @@
     <t>Invoice Expiration - Basic Claim After CIR</t>
   </si>
   <si>
-    <t>Automated\\InvoiceExpiration\\Basic\\ClaimHandledAfterCIR.feature</t>
+    <t>Automated\InvoiceExpiration\Basic\ClaimHandledAfterCIR.feature</t>
   </si>
   <si>
     <t>TC-125</t>
@@ -1154,7 +1157,7 @@
     <t>Invoice Expiration - Basic Digital After CIR</t>
   </si>
   <si>
-    <t>Automated\\InvoiceExpiration\\Basic\\DigitalClaimHandledAfterCIR.feature</t>
+    <t>Automated\InvoiceExpiration\Basic\DigitalClaimHandledAfterCIR.feature</t>
   </si>
   <si>
     <t>TC-126</t>
@@ -1163,7 +1166,7 @@
     <t>Invoice Expiration - Complete Claim to Bailiff</t>
   </si>
   <si>
-    <t>Automated\\InvoiceExpiration\\Complete\\ClaimSentToBailiffAfterCIR.feature</t>
+    <t>Automated\InvoiceExpiration\Complete\ClaimSentToBailiffAfterCIR.feature</t>
   </si>
   <si>
     <t>TC-127</t>
@@ -1172,7 +1175,7 @@
     <t>Invoice Expiration - Complete Digital to Bailiff</t>
   </si>
   <si>
-    <t>Automated\\InvoiceExpiration\\Complete\\DigitalClaimSentToBailiffAfterCIR.feature</t>
+    <t>Automated\InvoiceExpiration\Complete\DigitalClaimSentToBailiffAfterCIR.feature</t>
   </si>
   <si>
     <t>TC-128</t>
@@ -1181,7 +1184,7 @@
     <t>Invoice Expiration - Extended Claim to Bailiff</t>
   </si>
   <si>
-    <t>Automated\\InvoiceExpiration\\Extended\\ClaimSentToBailiffAfterCIR.feature</t>
+    <t>Automated\InvoiceExpiration\Extended\ClaimSentToBailiffAfterCIR.feature</t>
   </si>
   <si>
     <t>TC-129</t>
@@ -1211,7 +1214,7 @@
     <t>Matching - Assign Payments To Myself</t>
   </si>
   <si>
-    <t>Agent\\ToDo\\Matching\\AssignPaymentsToMyself.feature</t>
+    <t>Agent\ToDo\Matching\AssignPaymentsToMyself.feature</t>
   </si>
   <si>
     <t>TC-132</t>
@@ -1220,7 +1223,7 @@
     <t>Matching - Assign Selected Payments Summary</t>
   </si>
   <si>
-    <t>Agent\\ToDo\\Matching\\AssignSelectedPaymentsSummaryDialog.feature</t>
+    <t>Agent\ToDo\Matching\AssignSelectedPaymentsSummaryDialog.feature</t>
   </si>
   <si>
     <t>TC-133</t>
@@ -1229,7 +1232,7 @@
     <t>Matching - Duplicated Payments Buttons</t>
   </si>
   <si>
-    <t>Agent\\ToDo\\Matching\\DuplicatedPaymentsButtons.feature</t>
+    <t>Agent\ToDo\Matching\DuplicatedPaymentsButtons.feature</t>
   </si>
   <si>
     <t>TC-134</t>
@@ -1238,7 +1241,7 @@
     <t>Matching - Filter Payments</t>
   </si>
   <si>
-    <t>Agent\\ToDo\\Matching\\FilterPayments.feature</t>
+    <t>Agent\ToDo\Matching\FilterPayments.feature</t>
   </si>
   <si>
     <t>TC-135</t>
@@ -1247,7 +1250,7 @@
     <t>Matching - Full Text Search</t>
   </si>
   <si>
-    <t>Agent\\ToDo\\Matching\\FullTextSearch.feature</t>
+    <t>Agent\ToDo\Matching\FullTextSearch.feature</t>
   </si>
   <si>
     <t>TC-136</t>
@@ -1256,7 +1259,7 @@
     <t>Matching - Sort Payments</t>
   </si>
   <si>
-    <t>Agent\\ToDo\\Matching\\SortPayments.feature</t>
+    <t>Agent\ToDo\Matching\SortPayments.feature</t>
   </si>
   <si>
     <t>TC-137</t>
@@ -1265,7 +1268,7 @@
     <t>Matching - Start Matching Button</t>
   </si>
   <si>
-    <t>Agent\\ToDo\\Matching\\StartMatchingButton.feature</t>
+    <t>Agent\ToDo\Matching\StartMatchingButton.feature</t>
   </si>
   <si>
     <t>TC-138</t>
@@ -1274,7 +1277,7 @@
     <t>Matching - Forward Payment</t>
   </si>
   <si>
-    <t>Agent\\ToDo\\Matching\\ForwardPayment.feature</t>
+    <t>Agent\ToDo\Matching\ForwardPayment.feature</t>
   </si>
   <si>
     <t>TC-139</t>
@@ -1283,7 +1286,7 @@
     <t>Matching - Take Remaining as Profit</t>
   </si>
   <si>
-    <t>Agent\\ToDo\\Matching\\TakeRemainingAsProfit.feature</t>
+    <t>Agent\ToDo\Matching\TakeRemainingAsProfit.feature</t>
   </si>
   <si>
     <t>TC-140</t>
@@ -1295,7 +1298,7 @@
     <t>Reception</t>
   </si>
   <si>
-    <t>Agent\\ClaimFile\\AdminCode\\AdminCodeGDSFileName.feature</t>
+    <t>Agent\ClaimFile\AdminCode\AdminCodeGDSFileName.feature</t>
   </si>
   <si>
     <t>TC-141</t>
@@ -1304,7 +1307,7 @@
     <t>Admin Code in GDS Declaration No</t>
   </si>
   <si>
-    <t>Agent\\ClaimFile\\AdminCode\\AdminCodeInGDSDeclarationNo.feature</t>
+    <t>Agent\ClaimFile\AdminCode\AdminCodeInGDSDeclarationNo.feature</t>
   </si>
   <si>
     <t>TC-142</t>
@@ -1313,7 +1316,7 @@
     <t>Admin Code in LH File Name</t>
   </si>
   <si>
-    <t>Agent\\ClaimFile\\AdminCode\\AdminCodeInLHFileName.feature</t>
+    <t>Agent\ClaimFile\AdminCode\AdminCodeInLHFileName.feature</t>
   </si>
   <si>
     <t>TC-143</t>
@@ -1322,7 +1325,7 @@
     <t>No Admin Code in LH File Name</t>
   </si>
   <si>
-    <t>Agent\\ClaimFile\\AdminCode\\NoAdminCodeInLHFileName.feature</t>
+    <t>Agent\ClaimFile\AdminCode\NoAdminCodeInLHFileName.feature</t>
   </si>
   <si>
     <t>TC-144</t>
@@ -1331,7 +1334,7 @@
     <t>GDS Claim File with Correct BSN</t>
   </si>
   <si>
-    <t>Agent\\ClaimFile\\BSN\\GDSWithCorrectBSN.feature</t>
+    <t>Agent\ClaimFile\BSN\GDSWithCorrectBSN.feature</t>
   </si>
   <si>
     <t>TC-145</t>
@@ -1340,7 +1343,7 @@
     <t>GDS Claim File with Incorrect BSN</t>
   </si>
   <si>
-    <t>Agent\\ClaimFile\\BSN\\GDSWithIncorrectBSN.feature</t>
+    <t>Agent\ClaimFile\BSN\GDSWithIncorrectBSN.feature</t>
   </si>
   <si>
     <t>TC-146</t>
@@ -1349,7 +1352,7 @@
     <t>MZ Claim File with Correct BSN</t>
   </si>
   <si>
-    <t>Agent\\ClaimFile\\BSN\\MZWithCorrectBSN.feature</t>
+    <t>Agent\ClaimFile\BSN\MZWithCorrectBSN.feature</t>
   </si>
   <si>
     <t>TC-147</t>
@@ -1358,7 +1361,7 @@
     <t>MZ Claim File with Incorrect BSN</t>
   </si>
   <si>
-    <t>Agent\\ClaimFile\\BSN\\MZWithIncorrectBSN.feature</t>
+    <t>Agent\ClaimFile\BSN\MZWithIncorrectBSN.feature</t>
   </si>
   <si>
     <t>TC-148</t>
@@ -1367,7 +1370,7 @@
     <t>Process CHA Claim File - Agent (IM001)</t>
   </si>
   <si>
-    <t>Agent\\ClaimFile\\ProcessFile\\CHA_IM001.feature</t>
+    <t>Agent\ClaimFile\ProcessFile\CHA_IM001.feature</t>
   </si>
   <si>
     <t>TC-149</t>
@@ -1385,9 +1388,6 @@
     <t>Process Claim File - CHA_IM001</t>
   </si>
   <si>
-    <t>Agent\ClaimFile\ProcessFile\CHA_IM001.feature</t>
-  </si>
-  <si>
     <t>TC-151</t>
   </si>
   <si>
@@ -1421,7 +1421,7 @@
     <t>Download All Claim Files Report</t>
   </si>
   <si>
-    <t>Provider\\Report\\DownloadAllClaimFiles.feature</t>
+    <t>Provider\Report\DownloadAllClaimFiles.feature</t>
   </si>
   <si>
     <t>TC-155</t>
@@ -1433,7 +1433,7 @@
     <t>Templating &amp; Messaging</t>
   </si>
   <si>
-    <t>Agent\\Maintenance\\NotificationCSV.feature</t>
+    <t>Agent\Maintenance\NotificationCSV.feature</t>
   </si>
   <si>
     <t>TC-156</t>
@@ -1442,7 +1442,7 @@
     <t>TIM-Inzicht Notification Integration</t>
   </si>
   <si>
-    <t>Agent\\Maintenance\\NotificationTIMInzichtIntegration.feature</t>
+    <t>Agent\Maintenance\NotificationTIMInzichtIntegration.feature</t>
   </si>
   <si>
     <t>Functional</t>
@@ -1454,25 +1454,10 @@
     <t>E2E</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>Description</t>
-  </si>
-  <si>
-    <t>Agent TIM — pracownik biura</t>
-  </si>
-  <si>
-    <t>Provider Inzicht — placówka/lekarz</t>
-  </si>
-  <si>
-    <t>Patient — Payment Page</t>
-  </si>
-  <si>
-    <t>Admin — IAM / zarządzanie użytkownikami</t>
-  </si>
-  <si>
-    <t>System — testy automatyczne bez UI</t>
-  </si>
-  <si>
-    <t>Status</t>
   </si>
   <si>
     <t>Nie zaczęty</t>
@@ -2114,8 +2099,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7E337D7-9E96-492C-A995-A6BFDFEDAA79}">
-  <dimension ref="A1:L157"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE7985B-E7A9-4DBE-A0D9-601187D8F752}">
+  <dimension ref="A1:M157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
@@ -2129,9 +2114,10 @@
     <col min="9" max="9" width="60.7109375" customWidth="1"/>
     <col min="10" max="10" width="40.7109375" customWidth="1"/>
     <col min="11" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2168,3196 +2154,3199 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="G11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="G12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="G16" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="H16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" t="s">
         <v>45</v>
-      </c>
-      <c r="C12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" t="s">
-        <v>43</v>
-      </c>
-      <c r="H16" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" t="s">
         <v>73</v>
-      </c>
-      <c r="C22" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" t="s">
-        <v>16</v>
-      </c>
-      <c r="H22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B39" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C39" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B40" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" t="s">
+        <v>122</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" t="s">
         <v>120</v>
-      </c>
-      <c r="C40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H40" t="s">
-        <v>17</v>
-      </c>
-      <c r="I40" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C42" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B43" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C43" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B44" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C44" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C47" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C48" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B51" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C51" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B52" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C52" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E52" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H52" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B53" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C53" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B54" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C54" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H54" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B55" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C55" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H55" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C56" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H56" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B57" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C57" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H57" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B58" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C58" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H58" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B59" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C59" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H59" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B60" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C60" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H60" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B61" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C61" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G61" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B62" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C62" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G62" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B63" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C63" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G63" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H63" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B64" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C64" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I64" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B65" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C65" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I65" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B66" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C66" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H66" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B67" t="s">
+        <v>190</v>
+      </c>
+      <c r="C67" t="s">
+        <v>191</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G67" t="s">
+        <v>192</v>
+      </c>
+      <c r="H67" t="s">
         <v>189</v>
       </c>
-      <c r="C67" t="s">
-        <v>190</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G67" t="s">
-        <v>191</v>
-      </c>
-      <c r="H67" t="s">
-        <v>188</v>
-      </c>
       <c r="I67" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B68" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C68" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G68" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I68" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B69" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C69" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G69" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I69" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B70" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C70" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G70" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B71" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C71" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G71" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I71" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B72" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C72" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E72" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H72" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B73" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C73" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B74" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C74" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B75" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C75" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G75" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I75" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C76" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G76" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C77" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G77" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C78" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G78" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G79" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C80" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G80" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B81" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C81" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E81" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I81" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B82" t="s">
+        <v>230</v>
+      </c>
+      <c r="C82" t="s">
+        <v>231</v>
+      </c>
+      <c r="E82" t="s">
+        <v>208</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G82" t="s">
+        <v>24</v>
+      </c>
+      <c r="I82" t="s">
         <v>229</v>
-      </c>
-      <c r="C82" t="s">
-        <v>230</v>
-      </c>
-      <c r="E82" t="s">
-        <v>207</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G82" t="s">
-        <v>23</v>
-      </c>
-      <c r="I82" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C83" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D83" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H83" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I83" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C84" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D84" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H84" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C85" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D85" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H85" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C86" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D86" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H86" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B87" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C87" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D87" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H87" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I87" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B88" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C88" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D88" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H88" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C89" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D89" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H89" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C90" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D90" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H90" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C91" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D91" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H91" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D92" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H92" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C93" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D93" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I93" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B94" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D94" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H94" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B95" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C95" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D95" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H95" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C96" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D96" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H96" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B97" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C97" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D97" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H97" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B98" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C98" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D98" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H98" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B99" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C99" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D99" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H99" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I99" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B100" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C100" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D100" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H100" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B101" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C101" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D101" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H101" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I101" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B102" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C102" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D102" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H102" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I102" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B103" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C103" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D103" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H103" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I103" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B104" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C104" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D104" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H104" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I104" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B105" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C105" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D105" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H105" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C106" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D106" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H106" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I106" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C107" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D107" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H107" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I107" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B108" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C108" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D108" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H108" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I108" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B109" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C109" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D109" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H109" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I109" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B110" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C110" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D110" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I110" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B111" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C111" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D111" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H111" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B112" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C112" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D112" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H112" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I112" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B113" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C113" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D113" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H113" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I113" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B114" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C114" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D114" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H114" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I114" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B115" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C115" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D115" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H115" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I115" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B116" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C116" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D116" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H116" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B117" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C117" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D117" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H117" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B118" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C118" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D118" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H118" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I118" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B119" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C119" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D119" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H119" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I119" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B120" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C120" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D120" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H120" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I120" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B121" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C121" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D121" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H121" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B122" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C122" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D122" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H122" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I122" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B123" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C123" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D123" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H123" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B124" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C124" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D124" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H124" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I124" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B125" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C125" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D125" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H125" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I125" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C126" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D126" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H126" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I126" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B127" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C127" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D127" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H127" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I127" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B128" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C128" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D128" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H128" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I128" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B129" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C129" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D129" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H129" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I129" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B130" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C130" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D130" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H130" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B131" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C131" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D131" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H131" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I131" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C132" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D132" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E132" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H132" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I132" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B133" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C133" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D133" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H133" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I133" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B134" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C134" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H134" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I134" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B135" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C135" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D135" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H135" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B136" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D136" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H136" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C137" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D137" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H137" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I137" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B138" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C138" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D138" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H138" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I138" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B139" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C139" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D139" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H139" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B140" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C140" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D140" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H140" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I140" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B141" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C141" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D141" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H141" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I141" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B142" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C142" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D142" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H142" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I142" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B143" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C143" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D143" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H143" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I143" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B144" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C144" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D144" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H144" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I144" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B145" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C145" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D145" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H145" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I145" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B146" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C146" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D146" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H146" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B147" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C147" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H147" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I147" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B148" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C148" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D148" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H148" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I148" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B149" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C149" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D149" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H149" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I149" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B150" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C150" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D150" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H150" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I150" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B151" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C151" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H151" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I151" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B152" t="s">
         <v>446</v>
@@ -5366,13 +5355,13 @@
         <v>447</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H152" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I152" t="s">
         <v>448</v>
@@ -5380,7 +5369,7 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B153" t="s">
         <v>449</v>
@@ -5389,13 +5378,13 @@
         <v>450</v>
       </c>
       <c r="D153" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H153" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I153" t="s">
         <v>451</v>
@@ -5403,7 +5392,7 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B154" t="s">
         <v>452</v>
@@ -5412,13 +5401,13 @@
         <v>453</v>
       </c>
       <c r="D154" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H154" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I154" t="s">
         <v>454</v>
@@ -5426,7 +5415,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B155" t="s">
         <v>455</v>
@@ -5435,13 +5424,13 @@
         <v>456</v>
       </c>
       <c r="D155" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H155" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I155" t="s">
         <v>457</v>
@@ -5449,7 +5438,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B156" t="s">
         <v>458</v>
@@ -5461,10 +5450,10 @@
         <v>460</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H156" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I156" t="s">
         <v>461</v>
@@ -5472,7 +5461,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B157" t="s">
         <v>462</v>
@@ -5484,52 +5473,52 @@
         <v>460</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H157" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I157" t="s">
         <v>464</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1" xr:uid="{C7E337D7-9E96-492C-A995-A6BFDFEDAA79}"/>
+  <autoFilter ref="A1:M1" xr:uid="{FAE7985B-E7A9-4DBE-A0D9-601187D8F752}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{7922B5A7-4A41-46BC-9E45-B28A49929C56}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{D247B714-7BD8-4585-B8A1-1A8975AAB36A}">
           <x14:formula1>
             <xm:f>Actors!$A$2:$A$6</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{B7CBA8AC-4608-42E3-9EC5-B1E0B34005FC}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{D72E4E1D-86A3-4CCE-99D4-50BC128F5121}">
           <x14:formula1>
             <xm:f>Domains!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{9A2E40CD-CEDE-4501-9DAA-C23A4A572C06}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{7B090B23-6C6C-4EC2-B90F-2C1118726371}">
           <x14:formula1>
             <xm:f>Test_Types!$A$2:$A$6</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{FF3EA81F-D401-4EB7-9B6A-EF1F5CE18BB5}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{E36268CB-23A7-4247-82B4-9A120D55317C}">
           <x14:formula1>
             <xm:f>Status_Options!$A$1:$A$6</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{3565FC22-DC56-44E0-BD01-3548015BAEB8}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{6564340F-ACCA-44E7-B43F-E035A69974EC}">
           <x14:formula1>
             <xm:f>Team_Members!$A$2:$A$57</xm:f>
           </x14:formula1>
           <xm:sqref>G2:G157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{99C5D2DC-47A7-45B2-B45B-7089A47120D1}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{73A958BB-0D93-4BD8-A900-EF1FF39642E8}">
           <x14:formula1>
             <xm:f>Priorities!$A$2:$A$5</xm:f>
           </x14:formula1>
@@ -5542,7 +5531,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B13EF2ED-F7B7-4B9D-9E90-4AC6110B609B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B9FF1B5-6205-44D3-94C3-F486C8FF60E0}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5556,12 +5545,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -5585,60 +5574,41 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B6D594-57C4-432F-AC0F-E4E3623E5683}">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78AAABCF-BAF0-450D-BDB5-264AE256A124}">
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B5" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B6" t="s">
-        <v>473</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -5647,7 +5617,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAFC637A-74C2-414B-A32C-9ECB0A2FC336}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D826D2A4-65E7-4928-8A56-CFE41A54E7B1}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5657,58 +5627,58 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B6" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="B7" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -5717,7 +5687,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75E968FB-11E7-4DF8-875A-76FAF28DB2E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5776B112-F7A9-4A73-A7BB-C6C7D572AAD6}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5730,33 +5700,33 @@
         <v>7</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B4" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B5" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -5765,7 +5735,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{853ED996-B569-455B-8F58-B300E00C3F74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A01A0DD3-067D-4520-80B1-277ACDA692C7}">
   <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5779,37 +5749,37 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -5819,37 +5789,37 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -5858,7 +5828,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F12254-E0BB-4671-9ECA-DA68B9695C95}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{010F12C6-BD5F-487D-A2CB-19512198C22D}">
   <dimension ref="A1:A57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5867,287 +5837,287 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Scripts/PowerShell/TA_LIST_Sanity_Smoke/TA_Inventory.xlsx
+++ b/Scripts/PowerShell/TA_LIST_Sanity_Smoke/TA_Inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\SQL\SQL\TA_LIST_Sanity_Smoke\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AAB02FD-E5DA-47B0-9AF9-456E4FA9FC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C703AC0D-F4CA-4D9C-8D25-D102AD076D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2415" yWindow="1920" windowWidth="33840" windowHeight="18345" xr2:uid="{98A834BA-DB17-43E3-8C6F-F4CBDEBBF62B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{58F3F162-766D-4F31-A7F3-C7AA183242B3}"/>
   </bookViews>
   <sheets>
     <sheet name="TA_Report" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="545">
   <si>
     <t>Actor</t>
   </si>
@@ -1454,6 +1454,12 @@
     <t>E2E</t>
   </si>
   <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>Preparation</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -1482,6 +1488,12 @@
   </si>
   <si>
     <t>Wstrzymany</t>
+  </si>
+  <si>
+    <t>TO FIX</t>
+  </si>
+  <si>
+    <t>Do naprawy</t>
   </si>
   <si>
     <t>Suite</t>
@@ -2099,7 +2111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE7985B-E7A9-4DBE-A0D9-601187D8F752}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{041BDFD8-8FC2-4B45-9167-C0A71849DD70}">
   <dimension ref="A1:M157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5483,42 +5495,42 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1" xr:uid="{FAE7985B-E7A9-4DBE-A0D9-601187D8F752}"/>
+  <autoFilter ref="A1:M1" xr:uid="{041BDFD8-8FC2-4B45-9167-C0A71849DD70}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{D247B714-7BD8-4585-B8A1-1A8975AAB36A}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{76812D8E-F251-4B70-9260-20E741AED831}">
           <x14:formula1>
             <xm:f>Actors!$A$2:$A$6</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{D72E4E1D-86A3-4CCE-99D4-50BC128F5121}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{5B0DB244-A222-44CE-8748-7180081EE8EF}">
           <x14:formula1>
             <xm:f>Domains!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{7B090B23-6C6C-4EC2-B90F-2C1118726371}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{167A2EF8-3E8D-4CD5-872C-19D367D787F2}">
           <x14:formula1>
-            <xm:f>Test_Types!$A$2:$A$6</xm:f>
+            <xm:f>Test_Types!$A$2:$A$8</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{E36268CB-23A7-4247-82B4-9A120D55317C}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{E230D935-E4DB-471E-BFD4-FEF04203C185}">
           <x14:formula1>
-            <xm:f>Status_Options!$A$1:$A$6</xm:f>
+            <xm:f>Status_Options!$A$2:$A$8</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{6564340F-ACCA-44E7-B43F-E035A69974EC}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{81FB520B-39A8-4DC9-AA93-AC20980C16D0}">
           <x14:formula1>
             <xm:f>Team_Members!$A$2:$A$57</xm:f>
           </x14:formula1>
           <xm:sqref>G2:G157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{73A958BB-0D93-4BD8-A900-EF1FF39642E8}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{A17630B7-21AD-42E6-83AD-63ADDE402171}">
           <x14:formula1>
             <xm:f>Priorities!$A$2:$A$5</xm:f>
           </x14:formula1>
@@ -5531,11 +5543,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B9FF1B5-6205-44D3-94C3-F486C8FF60E0}">
-  <dimension ref="A1:A6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D56F1B12-2F80-401D-8026-D5758DAC2433}">
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -5566,6 +5578,16 @@
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>467</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -5574,7 +5596,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78AAABCF-BAF0-450D-BDB5-264AE256A124}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D96E4E72-EE2B-4924-86AF-16E26D44DDF7}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5617,8 +5639,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D826D2A4-65E7-4928-8A56-CFE41A54E7B1}">
-  <dimension ref="A1:B7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABD1FCD6-6D11-4DA7-98F4-309D6ADF8463}">
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -5627,10 +5649,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5638,7 +5660,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -5646,7 +5668,7 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -5654,7 +5676,7 @@
         <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -5662,23 +5684,31 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B7" t="s">
-        <v>477</v>
+        <v>479</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>480</v>
+      </c>
+      <c r="B8" t="s">
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -5687,7 +5717,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5776B112-F7A9-4A73-A7BB-C6C7D572AAD6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1201676A-0070-4D80-AA36-82D08D51EDE7}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5700,7 +5730,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5718,15 +5748,15 @@
         <v>235</v>
       </c>
       <c r="B4" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B5" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -5735,7 +5765,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A01A0DD3-067D-4520-80B1-277ACDA692C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A9EC9D-4B94-4960-91E2-9819E85AFFF8}">
   <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5749,7 +5779,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -5769,7 +5799,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -5779,7 +5809,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -5794,12 +5824,12 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -5809,7 +5839,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -5819,7 +5849,7 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -5828,7 +5858,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{010F12C6-BD5F-487D-A2CB-19512198C22D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D2DC8BA-C2ED-4663-B0A1-620736386478}">
   <dimension ref="A1:A57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5837,47 +5867,47 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
@@ -5887,37 +5917,37 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -5932,162 +5962,162 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
@@ -6097,22 +6127,22 @@
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">

--- a/Scripts/PowerShell/TA_LIST_Sanity_Smoke/TA_Inventory.xlsx
+++ b/Scripts/PowerShell/TA_LIST_Sanity_Smoke/TA_Inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\SQL\SQL\TA_LIST_Sanity_Smoke\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C703AC0D-F4CA-4D9C-8D25-D102AD076D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79BE4100-C168-47F2-8523-DABCC955E2FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{58F3F162-766D-4F31-A7F3-C7AA183242B3}"/>
+    <workbookView xWindow="2415" yWindow="1920" windowWidth="33840" windowHeight="18345" xr2:uid="{E70F5BB6-0474-4784-A5A0-A4BA71719E62}"/>
   </bookViews>
   <sheets>
     <sheet name="TA_Report" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="547">
   <si>
     <t>Actor</t>
   </si>
@@ -98,6 +98,9 @@
     <t>Stop on Claim in Inzicht</t>
   </si>
   <si>
+    <t>Claim Orchestration</t>
+  </si>
+  <si>
     <t>DONE</t>
   </si>
   <si>
@@ -173,6 +176,9 @@
     <t>Send claim to Clearing</t>
   </si>
   <si>
+    <t>Insurers</t>
+  </si>
+  <si>
     <t>Agent\Clearing\CreateIA100PercentPromise.feature</t>
   </si>
   <si>
@@ -182,6 +188,9 @@
     <t>Match Payment with a Claim</t>
   </si>
   <si>
+    <t>Banking</t>
+  </si>
+  <si>
     <t>Kamil Małysiak</t>
   </si>
   <si>
@@ -206,6 +215,9 @@
     <t>Create Payment Agreement</t>
   </si>
   <si>
+    <t>Invoicing &amp; Dunning</t>
+  </si>
+  <si>
     <t>Patient\Claim\PaymentAgreement\CreatePaymentAgreementDD.feature</t>
   </si>
   <si>
@@ -314,6 +326,9 @@
     <t>Add Message to BA from TIM</t>
   </si>
   <si>
+    <t>Templating &amp; Messaging</t>
+  </si>
+  <si>
     <t>Agent\Contact\MessageToBaFromTim.feature</t>
   </si>
   <si>
@@ -332,6 +347,9 @@
     <t>Settle any settlement</t>
   </si>
   <si>
+    <t>Factoring (w. Risk &amp; CHA)</t>
+  </si>
+  <si>
     <t>Sanity</t>
   </si>
   <si>
@@ -380,6 +398,9 @@
     <t>Login (TIM/Inzicht/IAM)</t>
   </si>
   <si>
+    <t>Auth &amp; User Management</t>
+  </si>
+  <si>
     <t>Agent\Login\LoginToTIM.feature</t>
   </si>
   <si>
@@ -410,6 +431,9 @@
     <t>Create Approval</t>
   </si>
   <si>
+    <t>Customer Configuration</t>
+  </si>
+  <si>
     <t>Agent\ToDo\Approvals\CreateResolveApproval-trzeba_rozdzielic.feature</t>
   </si>
   <si>
@@ -431,6 +455,9 @@
     <t>Upload claim file by Inzicht</t>
   </si>
   <si>
+    <t>Reception</t>
+  </si>
+  <si>
     <t>Provider\ClaimFile\UploadFile\SuccessfulUploadFileFromDeclarationsPage.feature</t>
   </si>
   <si>
@@ -698,6 +725,9 @@
     <t>Ledger Connector - Authorize Exact</t>
   </si>
   <si>
+    <t>Accounting (w. Ledger Connector)</t>
+  </si>
+  <si>
     <t>Provider\LedgerConnector\ConnectToExactLedgerConnector.feature</t>
   </si>
   <si>
@@ -752,9 +782,6 @@
     <t>Login to Inzicht</t>
   </si>
   <si>
-    <t>Auth &amp; User Management</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
@@ -812,9 +839,6 @@
     <t>Stop - Partial Stop Claim Lines</t>
   </si>
   <si>
-    <t>Claim Orchestration</t>
-  </si>
-  <si>
     <t>Provider\Claim\Stop\PartialStopClaimLines.feature</t>
   </si>
   <si>
@@ -1079,9 +1103,6 @@
     <t>Special Agreement Note</t>
   </si>
   <si>
-    <t>Customer Configuration</t>
-  </si>
-  <si>
     <t>Agent\BusinessAccount\SpecialAgreementNote.feature</t>
   </si>
   <si>
@@ -1091,9 +1112,6 @@
     <t>Copy Digital Invoice from Download Popup</t>
   </si>
   <si>
-    <t>Invoicing &amp; Dunning</t>
-  </si>
-  <si>
     <t>Patient\Claim\CreateCopy\CopyDigitalInvoiceFromDownloadInvoicePopup.feature</t>
   </si>
   <si>
@@ -1295,9 +1313,6 @@
     <t>Admin Code in GDS File Name</t>
   </si>
   <si>
-    <t>Reception</t>
-  </si>
-  <si>
     <t>Agent\ClaimFile\AdminCode\AdminCodeGDSFileName.feature</t>
   </si>
   <si>
@@ -1430,9 +1445,6 @@
     <t>Notification CSV Export</t>
   </si>
   <si>
-    <t>Templating &amp; Messaging</t>
-  </si>
-  <si>
     <t>Agent\Maintenance\NotificationCSV.feature</t>
   </si>
   <si>
@@ -1508,25 +1520,19 @@
     <t>SMOKE</t>
   </si>
   <si>
-    <t>Factoring (w. Risk &amp; CHA)</t>
-  </si>
-  <si>
     <t>Vendor API</t>
   </si>
   <si>
-    <t>Insurers</t>
-  </si>
-  <si>
     <t>Bailiff</t>
   </si>
   <si>
-    <t>Banking</t>
-  </si>
-  <si>
-    <t>Accounting (w. Ledger Connector)</t>
-  </si>
-  <si>
     <t>Frontend Infrastructure</t>
+  </si>
+  <si>
+    <t>BIDataCollector</t>
+  </si>
+  <si>
+    <t>Validation</t>
   </si>
   <si>
     <t>Name</t>
@@ -2111,14 +2117,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{041BDFD8-8FC2-4B45-9167-C0A71849DD70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F063C09E-1E87-4162-9525-C1074A49151D}">
   <dimension ref="A1:M157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="88.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2180,74 +2186,77 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
       <c r="F2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -2255,36 +2264,36 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -2292,417 +2301,462 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
         <v>46</v>
       </c>
-      <c r="C12" t="s">
+      <c r="F12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" t="s">
-        <v>44</v>
-      </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>55</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>58</v>
+      </c>
+      <c r="D14" t="s">
+        <v>55</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>61</v>
+      </c>
+      <c r="D15" t="s">
+        <v>55</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>46</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I16" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>71</v>
+      </c>
+      <c r="D19" t="s">
+        <v>42</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>73</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I20" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>42</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I21" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>79</v>
+      </c>
+      <c r="D22" t="s">
+        <v>42</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I22" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>81</v>
+      </c>
+      <c r="D23" t="s">
+        <v>42</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I23" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>84</v>
+      </c>
+      <c r="D24" t="s">
+        <v>42</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I24" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>91</v>
+      </c>
+      <c r="D27" t="s">
+        <v>92</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I27" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -2710,253 +2764,277 @@
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>95</v>
+      </c>
+      <c r="D28" t="s">
+        <v>92</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I28" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>98</v>
+      </c>
+      <c r="D29" t="s">
+        <v>99</v>
       </c>
       <c r="E29" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I29" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>105</v>
+      </c>
+      <c r="D31" t="s">
+        <v>55</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I31" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>110</v>
+      </c>
+      <c r="D33" t="s">
+        <v>99</v>
       </c>
       <c r="E33" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I33" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>115</v>
+      </c>
+      <c r="D35" t="s">
+        <v>116</v>
       </c>
       <c r="E35" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I35" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C36" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C37" t="s">
-        <v>114</v>
+        <v>121</v>
+      </c>
+      <c r="D37" t="s">
+        <v>92</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I37" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C38" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>126</v>
+      </c>
+      <c r="D39" t="s">
+        <v>127</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I39" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>130</v>
+      </c>
+      <c r="D40" t="s">
+        <v>127</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I40" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -2964,16 +3042,16 @@
         <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2981,507 +3059,552 @@
         <v>13</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C42" t="s">
-        <v>126</v>
+        <v>134</v>
+      </c>
+      <c r="D42" t="s">
+        <v>135</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I42" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C43" t="s">
-        <v>129</v>
+        <v>138</v>
+      </c>
+      <c r="D43" t="s">
+        <v>135</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I43" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C44" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B45" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C45" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C46" t="s">
-        <v>137</v>
+        <v>146</v>
+      </c>
+      <c r="D46" t="s">
+        <v>135</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I46" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C47" t="s">
-        <v>140</v>
+        <v>149</v>
+      </c>
+      <c r="D47" t="s">
+        <v>16</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I47" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B48" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C48" t="s">
-        <v>143</v>
+        <v>152</v>
+      </c>
+      <c r="D48" t="s">
+        <v>92</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I48" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C49" t="s">
-        <v>146</v>
+        <v>155</v>
+      </c>
+      <c r="D49" t="s">
+        <v>55</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I49" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B50" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C50" t="s">
-        <v>149</v>
+        <v>158</v>
+      </c>
+      <c r="D50" t="s">
+        <v>135</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G50" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="H50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I50" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B51" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C51" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B52" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C52" t="s">
-        <v>155</v>
+        <v>164</v>
+      </c>
+      <c r="D52" t="s">
+        <v>99</v>
       </c>
       <c r="E52" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G52" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="H52" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I52" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B53" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C53" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H53" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B54" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C54" t="s">
-        <v>159</v>
+        <v>168</v>
+      </c>
+      <c r="D54" t="s">
+        <v>55</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H54" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I54" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B55" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C55" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H55" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C56" t="s">
-        <v>164</v>
+        <v>173</v>
+      </c>
+      <c r="D56" t="s">
+        <v>55</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H56" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I56" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B57" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C57" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H57" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B58" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C58" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H58" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B59" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C59" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H59" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C60" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H60" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C61" t="s">
-        <v>174</v>
+        <v>183</v>
+      </c>
+      <c r="D61" t="s">
+        <v>42</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H61" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I61" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C62" t="s">
-        <v>176</v>
+        <v>185</v>
+      </c>
+      <c r="D62" t="s">
+        <v>55</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H62" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I62" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B63" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="C63" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G63" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H63" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B64" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C64" t="s">
-        <v>181</v>
+        <v>190</v>
+      </c>
+      <c r="D64" t="s">
+        <v>55</v>
       </c>
       <c r="I64" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B65" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>184</v>
+        <v>193</v>
+      </c>
+      <c r="D65" t="s">
+        <v>55</v>
       </c>
       <c r="I65" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B66" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C66" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H66" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B67" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="C67" t="s">
-        <v>191</v>
+        <v>200</v>
+      </c>
+      <c r="D67" t="s">
+        <v>55</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G67" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="H67" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="I67" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -3489,19 +3612,22 @@
         <v>13</v>
       </c>
       <c r="B68" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="C68" t="s">
-        <v>195</v>
+        <v>204</v>
+      </c>
+      <c r="D68" t="s">
+        <v>135</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G68" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="I68" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -3509,36 +3635,39 @@
         <v>13</v>
       </c>
       <c r="B69" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C69" t="s">
-        <v>199</v>
+        <v>208</v>
+      </c>
+      <c r="D69" t="s">
+        <v>135</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G69" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="I69" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B70" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C70" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G70" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -3546,45 +3675,51 @@
         <v>13</v>
       </c>
       <c r="B71" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C71" t="s">
+        <v>214</v>
+      </c>
+      <c r="D71" t="s">
+        <v>135</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G71" t="s">
         <v>205</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G71" t="s">
-        <v>196</v>
-      </c>
       <c r="I71" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B72" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="C72" t="s">
-        <v>207</v>
+        <v>216</v>
+      </c>
+      <c r="D72" t="s">
+        <v>16</v>
       </c>
       <c r="E72" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G72" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I72" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -3592,13 +3727,13 @@
         <v>13</v>
       </c>
       <c r="B73" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C73" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -3606,13 +3741,13 @@
         <v>13</v>
       </c>
       <c r="B74" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="C74" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
@@ -3620,19 +3755,22 @@
         <v>13</v>
       </c>
       <c r="B75" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C75" t="s">
-        <v>215</v>
+        <v>224</v>
+      </c>
+      <c r="D75" t="s">
+        <v>225</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G75" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I75" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -3640,16 +3778,16 @@
         <v>13</v>
       </c>
       <c r="B76" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C76" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G76" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -3657,16 +3795,16 @@
         <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C77" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G77" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -3674,16 +3812,16 @@
         <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C78" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G78" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -3691,16 +3829,16 @@
         <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C79" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G79" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -3708,62 +3846,68 @@
         <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C80" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G80" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B81" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C81" t="s">
-        <v>228</v>
+        <v>238</v>
+      </c>
+      <c r="D81" t="s">
+        <v>16</v>
       </c>
       <c r="E81" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G81" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I81" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B82" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C82" t="s">
-        <v>231</v>
+        <v>241</v>
+      </c>
+      <c r="D82" t="s">
+        <v>16</v>
       </c>
       <c r="E82" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G82" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I82" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -3771,22 +3915,22 @@
         <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="C83" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D83" t="s">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H83" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="I83" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -3794,22 +3938,22 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C84" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D84" t="s">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H84" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I84" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
@@ -3817,22 +3961,22 @@
         <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C85" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="D85" t="s">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H85" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I85" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -3840,68 +3984,68 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="C86" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="D86" t="s">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H86" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I86" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B87" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C87" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="D87" t="s">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H87" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="I87" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B88" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="C88" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="D88" t="s">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H88" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I88" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -3909,22 +4053,22 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C89" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D89" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H89" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I89" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -3932,22 +4076,22 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C90" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="D90" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H90" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I90" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
@@ -3955,22 +4099,22 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C91" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D91" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H91" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I91" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -3978,22 +4122,22 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C92" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D92" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H92" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I92" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -4001,68 +4145,68 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C93" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D93" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H93" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I93" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B94" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C94" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D94" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H94" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I94" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B95" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C95" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D95" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H95" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I95" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -4070,229 +4214,229 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C96" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D96" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H96" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I96" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B97" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C97" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D97" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H97" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I97" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B98" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C98" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D98" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H98" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I98" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B99" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C99" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D99" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H99" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I99" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B100" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C100" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="D100" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H100" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I100" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B101" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C101" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D101" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H101" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I101" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B102" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C102" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D102" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H102" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I102" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B103" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C103" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="D103" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H103" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I103" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B104" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C104" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="D104" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H104" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I104" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B105" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C105" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D105" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H105" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I105" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
@@ -4300,22 +4444,22 @@
         <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C106" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="D106" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H106" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I106" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -4323,22 +4467,22 @@
         <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="C107" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D107" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H107" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I107" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
@@ -4346,22 +4490,22 @@
         <v>13</v>
       </c>
       <c r="B108" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C108" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D108" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H108" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I108" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
@@ -4369,91 +4513,91 @@
         <v>13</v>
       </c>
       <c r="B109" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C109" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="D109" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H109" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I109" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B110" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C110" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="D110" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H110" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I110" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B111" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C111" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="D111" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H111" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I111" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B112" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C112" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D112" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H112" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I112" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -4461,22 +4605,22 @@
         <v>13</v>
       </c>
       <c r="B113" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C113" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="D113" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H113" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="I113" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -4484,22 +4628,22 @@
         <v>13</v>
       </c>
       <c r="B114" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C114" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D114" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H114" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="I114" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -4507,807 +4651,807 @@
         <v>13</v>
       </c>
       <c r="B115" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C115" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="D115" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H115" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="I115" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B116" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C116" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="D116" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H116" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I116" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B117" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C117" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="D117" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H117" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I117" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B118" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C118" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="D118" t="s">
-        <v>343</v>
+        <v>127</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H118" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I118" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B119" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C119" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="D119" t="s">
-        <v>347</v>
+        <v>55</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H119" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I119" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B120" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C120" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D120" t="s">
-        <v>347</v>
+        <v>55</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H120" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I120" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B121" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C121" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D121" t="s">
-        <v>347</v>
+        <v>55</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H121" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I121" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B122" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C122" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="D122" t="s">
-        <v>347</v>
+        <v>55</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H122" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I122" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B123" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C123" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D123" t="s">
-        <v>347</v>
+        <v>55</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H123" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I123" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B124" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C124" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D124" t="s">
-        <v>347</v>
+        <v>55</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H124" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I124" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B125" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C125" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D125" t="s">
-        <v>347</v>
+        <v>55</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H125" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="I125" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B126" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C126" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="D126" t="s">
-        <v>347</v>
+        <v>55</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H126" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="I126" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B127" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C127" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D127" t="s">
-        <v>347</v>
+        <v>55</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H127" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="I127" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B128" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C128" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="D128" t="s">
-        <v>347</v>
+        <v>55</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H128" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="I128" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B129" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C129" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="D129" t="s">
-        <v>347</v>
+        <v>55</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H129" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="I129" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B130" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C130" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="D130" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H130" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I130" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B131" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C131" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D131" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H131" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I131" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B132" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C132" t="s">
+        <v>393</v>
+      </c>
+      <c r="D132" t="s">
         <v>387</v>
       </c>
-      <c r="D132" t="s">
-        <v>381</v>
-      </c>
       <c r="E132" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H132" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I132" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B133" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C133" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D133" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H133" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I133" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B134" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C134" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="D134" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H134" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I134" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B135" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C135" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="D135" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H135" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I135" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B136" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C136" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="D136" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H136" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I136" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B137" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C137" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D137" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H137" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I137" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B138" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C138" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D138" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H138" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I138" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B139" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C139" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="D139" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H139" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I139" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B140" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C140" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D140" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H140" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I140" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B141" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C141" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D141" t="s">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H141" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I141" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B142" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C142" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D142" t="s">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H142" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I142" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B143" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C143" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D143" t="s">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H143" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I143" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B144" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C144" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D144" t="s">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H144" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I144" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B145" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C145" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D145" t="s">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H145" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I145" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B146" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C146" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D146" t="s">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H146" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I146" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B147" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C147" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D147" t="s">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H147" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I147" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B148" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C148" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H148" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I148" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B149" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C149" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D149" t="s">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H149" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I149" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
@@ -5315,45 +5459,45 @@
         <v>13</v>
       </c>
       <c r="B150" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C150" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D150" t="s">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H150" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I150" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B151" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C151" t="s">
+        <v>450</v>
+      </c>
+      <c r="D151" t="s">
+        <v>135</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H151" t="s">
+        <v>19</v>
+      </c>
+      <c r="I151" t="s">
         <v>445</v>
-      </c>
-      <c r="D151" t="s">
-        <v>415</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H151" t="s">
-        <v>18</v>
-      </c>
-      <c r="I151" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
@@ -5361,22 +5505,22 @@
         <v>13</v>
       </c>
       <c r="B152" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C152" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H152" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I152" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
@@ -5384,22 +5528,22 @@
         <v>13</v>
       </c>
       <c r="B153" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C153" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H153" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I153" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
@@ -5407,22 +5551,22 @@
         <v>13</v>
       </c>
       <c r="B154" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C154" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D154" t="s">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H154" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I154" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
@@ -5430,107 +5574,107 @@
         <v>13</v>
       </c>
       <c r="B155" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C155" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D155" t="s">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H155" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I155" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B156" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C156" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D156" t="s">
-        <v>460</v>
+        <v>92</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H156" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I156" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B157" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C157" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D157" t="s">
-        <v>460</v>
+        <v>92</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H157" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I157" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1" xr:uid="{041BDFD8-8FC2-4B45-9167-C0A71849DD70}"/>
+  <autoFilter ref="A1:M1" xr:uid="{F063C09E-1E87-4162-9525-C1074A49151D}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{76812D8E-F251-4B70-9260-20E741AED831}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{F1335E73-0468-482D-AB69-60E33C80FD97}">
           <x14:formula1>
             <xm:f>Actors!$A$2:$A$6</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{5B0DB244-A222-44CE-8748-7180081EE8EF}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{9156A3C8-3646-4AB2-9CD8-FAD9E9EDBB58}">
           <x14:formula1>
-            <xm:f>Domains!$A$2:$A$16</xm:f>
+            <xm:f>Domains!$A$2:$A$18</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{167A2EF8-3E8D-4CD5-872C-19D367D787F2}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{DC369BB2-3BE1-496D-AE0D-834A005ACFF6}">
           <x14:formula1>
             <xm:f>Test_Types!$A$2:$A$8</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{E230D935-E4DB-471E-BFD4-FEF04203C185}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{63DDE378-0FF2-4593-A11B-EEC8B44888CE}">
           <x14:formula1>
             <xm:f>Status_Options!$A$2:$A$8</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{81FB520B-39A8-4DC9-AA93-AC20980C16D0}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{34A47905-1027-4833-81C4-D652AE03F545}">
           <x14:formula1>
             <xm:f>Team_Members!$A$2:$A$57</xm:f>
           </x14:formula1>
           <xm:sqref>G2:G157</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{A17630B7-21AD-42E6-83AD-63ADDE402171}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{79C60A82-B1F1-4493-AD13-FA560010F98B}">
           <x14:formula1>
             <xm:f>Priorities!$A$2:$A$5</xm:f>
           </x14:formula1>
@@ -5543,7 +5687,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D56F1B12-2F80-401D-8026-D5758DAC2433}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BA40D2E-5143-4EAC-9016-86D39A98A44F}">
   <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5557,37 +5701,37 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -5596,7 +5740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D96E4E72-EE2B-4924-86AF-16E26D44DDF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D0BB77C-99EE-4078-B7A9-972614AD87D7}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5610,7 +5754,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -5620,17 +5764,17 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -5639,7 +5783,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABD1FCD6-6D11-4DA7-98F4-309D6ADF8463}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46EF4DF5-4EE0-40CB-B386-2BA3B28446E3}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5649,66 +5793,66 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B6" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B7" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B8" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -5717,7 +5861,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1201676A-0070-4D80-AA36-82D08D51EDE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B047E70-7F65-41E1-ADD3-B7BA1B41BEAB}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5730,33 +5874,33 @@
         <v>7</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B4" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B5" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -5765,8 +5909,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A9EC9D-4B94-4960-91E2-9819E85AFFF8}">
-  <dimension ref="A1:A16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{999BA1EA-D627-418D-9005-9CEC6AA1781C}">
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
@@ -5779,77 +5923,87 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>486</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>343</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>415</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>488</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>460</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>347</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>490</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>491</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>234</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>492</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -5858,7 +6012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D2DC8BA-C2ED-4663-B0A1-620736386478}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{043F794C-00F7-4912-99BE-7D560C8F0D3B}">
   <dimension ref="A1:A57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5867,287 +6021,287 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Scripts/PowerShell/TA_LIST_Sanity_Smoke/TA_Inventory.xlsx
+++ b/Scripts/PowerShell/TA_LIST_Sanity_Smoke/TA_Inventory.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\SQL\SQL\TA_LIST_Sanity_Smoke\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SQL\SQL\TA_LIST_Sanity_Smoke\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79BE4100-C168-47F2-8523-DABCC955E2FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E740A8E0-F9BD-45AF-B075-C01F618AB312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2415" yWindow="1920" windowWidth="33840" windowHeight="18345" xr2:uid="{E70F5BB6-0474-4784-A5A0-A4BA71719E62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{9994AA82-A7E9-4F79-9C33-43EAE1F304F4}"/>
   </bookViews>
   <sheets>
     <sheet name="TA_Report" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="562">
   <si>
     <t>Actor</t>
   </si>
@@ -1689,13 +1689,58 @@
   </si>
   <si>
     <t>Tomasz Smerdzyński</t>
+  </si>
+  <si>
+    <t>TIMUI Provider ToDo - Checking Bad Files notes</t>
+  </si>
+  <si>
+    <t>TIMUI Provider ToDo - Resolving  Bad Files notes</t>
+  </si>
+  <si>
+    <t>TC-157</t>
+  </si>
+  <si>
+    <t>TC-158</t>
+  </si>
+  <si>
+    <t>TC-159</t>
+  </si>
+  <si>
+    <t>TC-160</t>
+  </si>
+  <si>
+    <t>TC-161</t>
+  </si>
+  <si>
+    <t>TC-162</t>
+  </si>
+  <si>
+    <t>TC-163</t>
+  </si>
+  <si>
+    <t>TC-164</t>
+  </si>
+  <si>
+    <t>TC-165</t>
+  </si>
+  <si>
+    <t>TC-166</t>
+  </si>
+  <si>
+    <t>TC-167</t>
+  </si>
+  <si>
+    <t>TC-168</t>
+  </si>
+  <si>
+    <t>TC-169</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1718,6 +1763,13 @@
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1788,7 +1840,57 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFADD8E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD6BAEB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2117,8 +2219,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F063C09E-1E87-4162-9525-C1074A49151D}">
-  <dimension ref="A1:M157"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B30F859-36C4-4223-A559-BE35C962BFED}">
+  <dimension ref="A1:M170"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
@@ -2129,7 +2231,7 @@
     <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="60.7109375" customWidth="1"/>
+    <col min="9" max="9" width="82.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="40.7109375" customWidth="1"/>
     <col min="11" max="12" width="12.7109375" customWidth="1"/>
     <col min="13" max="13" width="20.7109375" customWidth="1"/>
@@ -5638,47 +5740,172 @@
         <v>468</v>
       </c>
     </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>21</v>
+      </c>
+      <c r="B158" t="s">
+        <v>549</v>
+      </c>
+      <c r="C158" t="s">
+        <v>547</v>
+      </c>
+      <c r="D158" t="s">
+        <v>135</v>
+      </c>
+      <c r="F158" t="s">
+        <v>24</v>
+      </c>
+      <c r="G158" t="s">
+        <v>205</v>
+      </c>
+      <c r="H158" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>21</v>
+      </c>
+      <c r="B159" t="s">
+        <v>550</v>
+      </c>
+      <c r="C159" t="s">
+        <v>548</v>
+      </c>
+      <c r="D159" t="s">
+        <v>135</v>
+      </c>
+      <c r="F159" t="s">
+        <v>24</v>
+      </c>
+      <c r="G159" t="s">
+        <v>205</v>
+      </c>
+      <c r="H159" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B160" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B163" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B165" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B166" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B167" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B168" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B169" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B170" t="s">
+        <v>561</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M1" xr:uid="{F063C09E-1E87-4162-9525-C1074A49151D}"/>
+  <autoFilter ref="A1:M1" xr:uid="{9B30F859-36C4-4223-A559-BE35C962BFED}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="F2:F500">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+      <formula>"TODO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+      <formula>"IN PROGRESS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+      <formula>"ALMOST"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"DONE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+      <formula>"BLOCKED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+      <formula>"ON HOLD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+      <formula>"TO FIX"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{F1335E73-0468-482D-AB69-60E33C80FD97}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{92457D2B-9A03-4403-AD01-66EEA027C617}">
           <x14:formula1>
-            <xm:f>Actors!$A$2:$A$6</xm:f>
+            <xm:f>Actors!$A$2:$A$7</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A157</xm:sqref>
+          <xm:sqref>A2:A500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{9156A3C8-3646-4AB2-9CD8-FAD9E9EDBB58}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{4CC62A10-E718-442C-B799-0F16CAF3F096}">
           <x14:formula1>
-            <xm:f>Domains!$A$2:$A$18</xm:f>
+            <xm:f>Domains!$A$2:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D157</xm:sqref>
+          <xm:sqref>D2:D500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{DC369BB2-3BE1-496D-AE0D-834A005ACFF6}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{5E0C49D6-02EB-40A1-B50F-CFCE7716F054}">
           <x14:formula1>
-            <xm:f>Test_Types!$A$2:$A$8</xm:f>
+            <xm:f>Test_Types!$A$2:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E157</xm:sqref>
+          <xm:sqref>E2:E500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{63DDE378-0FF2-4593-A11B-EEC8B44888CE}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{08CB0EF8-E0DA-4EC1-9C1A-0160D2F2DAA4}">
           <x14:formula1>
-            <xm:f>Status_Options!$A$2:$A$8</xm:f>
+            <xm:f>Status_Options!$A$2:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F157</xm:sqref>
+          <xm:sqref>F2:F500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{34A47905-1027-4833-81C4-D652AE03F545}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{07A8869C-ABD9-4664-AA76-03C1A42D5CA9}">
           <x14:formula1>
-            <xm:f>Team_Members!$A$2:$A$57</xm:f>
+            <xm:f>Team_Members!$A$2:$A$58</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G157</xm:sqref>
+          <xm:sqref>G2:G500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{79C60A82-B1F1-4493-AD13-FA560010F98B}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{7E3B4E90-7DDF-4C83-A6A0-C9E172DD02DF}">
           <x14:formula1>
-            <xm:f>Priorities!$A$2:$A$5</xm:f>
+            <xm:f>Priorities!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H157</xm:sqref>
+          <xm:sqref>H2:H500</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5687,8 +5914,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BA40D2E-5143-4EAC-9016-86D39A98A44F}">
-  <dimension ref="A1:A8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7496E67-3B6B-482B-86BD-EB3CEAD22C10}">
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -5699,38 +5926,38 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>100</v>
-      </c>
-    </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>217</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>469</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>473</v>
       </c>
     </row>
@@ -5740,8 +5967,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D0BB77C-99EE-4078-B7A9-972614AD87D7}">
-  <dimension ref="A1:A6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{954913FB-9996-4F10-BB26-E1FBE5F9D91A}">
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
@@ -5752,28 +5979,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-    </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>195</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>140</v>
       </c>
     </row>
@@ -5783,8 +6010,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46EF4DF5-4EE0-40CB-B386-2BA3B28446E3}">
-  <dimension ref="A1:B8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{812D383D-1036-44AD-A774-7C284EB85C2D}">
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -5799,59 +6026,59 @@
         <v>475</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>476</v>
-      </c>
-    </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>480</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B7" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>482</v>
+      </c>
+      <c r="B8" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>484</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>485</v>
       </c>
     </row>
@@ -5861,8 +6088,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B047E70-7F65-41E1-ADD3-B7BA1B41BEAB}">
-  <dimension ref="A1:B5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE462599-8991-4044-B603-F4878AE55786}">
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
@@ -5877,29 +6104,29 @@
         <v>486</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>198</v>
-      </c>
-    </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B4" t="s">
-        <v>487</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B5" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>488</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>489</v>
       </c>
     </row>
@@ -5909,8 +6136,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{999BA1EA-D627-418D-9005-9CEC6AA1781C}">
-  <dimension ref="A1:A18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17A1275-A07C-42CA-9D65-F2247F5B9287}">
+  <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
@@ -5921,88 +6148,88 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>99</v>
-      </c>
-    </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>344</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>490</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>491</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>491</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>387</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>225</v>
+        <v>387</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>492</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>494</v>
       </c>
     </row>
@@ -6012,8 +6239,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{043F794C-00F7-4912-99BE-7D560C8F0D3B}">
-  <dimension ref="A1:A57"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D230F4-CC0B-4FF8-8AFB-91700E1E4B32}">
+  <dimension ref="A1:A58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
@@ -6024,283 +6251,283 @@
         <v>495</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>496</v>
-      </c>
-    </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>504</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>159</v>
+        <v>510</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>511</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>205</v>
+        <v>542</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>543</v>
+        <v>205</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>18</v>
       </c>
     </row>
